--- a/工资条模板.xlsx
+++ b/工资条模板.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="工资条模板" sheetId="1" r:id="rId1"/>
@@ -27,13 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
-  <si>
-    <t>如有异常</t>
-  </si>
-  <si>
-    <t>请在6号前反馈</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>姓名</t>
   </si>
@@ -714,12 +708,9 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1257,129 +1248,115 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="7"/>
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="10.875" customWidth="1"/>
     <col min="2" max="2" width="13.375" customWidth="1"/>
     <col min="3" max="8" width="10.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27" spans="1:8">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>9</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="1">
+        <v>8000</v>
+      </c>
+      <c r="E2" s="1">
+        <v>1200</v>
+      </c>
+      <c r="F2" s="1">
+        <v>300</v>
+      </c>
+      <c r="G2" s="1">
+        <v>100</v>
+      </c>
+      <c r="H2" s="1">
+        <v>9400</v>
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="2">
-        <v>8000</v>
-      </c>
-      <c r="E3" s="2">
-        <v>1200</v>
-      </c>
-      <c r="F3" s="2">
-        <v>300</v>
-      </c>
-      <c r="G3" s="2">
-        <v>100</v>
-      </c>
-      <c r="H3" s="2">
-        <v>9400</v>
+      <c r="C3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="1">
+        <v>7000</v>
+      </c>
+      <c r="E3" s="1">
+        <v>1000</v>
+      </c>
+      <c r="F3" s="1">
+        <v>200</v>
+      </c>
+      <c r="G3" s="1">
+        <v>50</v>
+      </c>
+      <c r="H3" s="1">
+        <v>8150</v>
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="2">
-        <v>7000</v>
-      </c>
-      <c r="E4" s="2">
-        <v>1000</v>
-      </c>
-      <c r="F4" s="2">
-        <v>200</v>
-      </c>
-      <c r="G4" s="2">
-        <v>50</v>
-      </c>
-      <c r="H4" s="2">
-        <v>8150</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="2">
+      <c r="D4" s="1">
         <v>6500</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E4" s="1">
         <v>900</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F4" s="1">
         <v>150</v>
       </c>
-      <c r="G5" s="2">
+      <c r="G4" s="1">
         <v>0</v>
       </c>
-      <c r="H5" s="2">
+      <c r="H4" s="1">
         <v>7550</v>
       </c>
     </row>
